--- a/HeyHomie_Website_Page_Inventory.xlsx
+++ b/HeyHomie_Website_Page_Inventory.xlsx
@@ -1,20 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="PAGE INVENTORY" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="PAGE DETAILS" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="DIRECT LINKS" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="SEO" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="GOOGLE ADS" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="ANALYTICS" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="TESTING" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="CHANGELOG" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PAGE INVENTORY" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PAGE DETAILS" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="DIRECT LINKS" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SEO" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="GOOGLE ADS" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ANALYTICS" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TESTING" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CHANGELOG" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CITY FAQ CONTENT" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -260,7 +261,7 @@
 </file>
 
 <file path=xl/tables/table7.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="7" name="TESTING" displayName="TESTING" ref="A1:G27" headerRowCount="1">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="7" name="TESTING" displayName="TESTING" ref="A1:G35" headerRowCount="1">
   <autoFilter ref="A1:G27"/>
   <tableColumns count="7">
     <tableColumn id="1" name="Page ID"/>
@@ -276,7 +277,7 @@
 </file>
 
 <file path=xl/tables/table8.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="8" name="CHANGELOG" displayName="CHANGELOG" ref="A1:G12" headerRowCount="1">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="8" name="CHANGELOG" displayName="CHANGELOG" ref="A1:G14" headerRowCount="1">
   <autoFilter ref="A1:G12"/>
   <tableColumns count="7">
     <tableColumn id="1" name="Date"/>
@@ -288,6 +289,20 @@
     <tableColumn id="7" name="Evidence"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight9" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table9.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="9" name="CITY_FAQ_CONTENT" displayName="CITY_FAQ_CONTENT" ref="A1:E22" headerRowCount="1">
+  <autoFilter ref="A1:E22"/>
+  <tableColumns count="5">
+    <tableColumn id="1" name="#"/>
+    <tableColumn id="2" name="Question (PL)"/>
+    <tableColumn id="3" name="Question (EN)"/>
+    <tableColumn id="4" name="City-adaptive?"/>
+    <tableColumn id="5" name="Notes"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleLight9" showRowStripes="1"/>
 </table>
 </file>
 
@@ -821,7 +836,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>Updated in repo — NOT DEPLOYED</t>
+          <t>Content expanded in repo — NOT DEPLOYED</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -841,7 +856,7 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-07-26</t>
         </is>
       </c>
     </row>
@@ -883,7 +898,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>Updated in repo — NOT DEPLOYED</t>
+          <t>Content expanded in repo — NOT DEPLOYED</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -903,7 +918,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-07-26</t>
         </is>
       </c>
     </row>
@@ -945,7 +960,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>Updated in repo — NOT DEPLOYED</t>
+          <t>Content expanded in repo — NOT DEPLOYED</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -965,7 +980,7 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-07-26</t>
         </is>
       </c>
     </row>
@@ -1007,7 +1022,7 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>Updated in repo — NOT DEPLOYED</t>
+          <t>Content expanded in repo — NOT DEPLOYED</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -1027,7 +1042,7 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-07-26</t>
         </is>
       </c>
     </row>
@@ -1069,7 +1084,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>Updated in repo — NOT DEPLOYED</t>
+          <t>Content expanded in repo — NOT DEPLOYED</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1089,7 +1104,7 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-07-26</t>
         </is>
       </c>
     </row>
@@ -1131,7 +1146,7 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>Updated in repo — NOT DEPLOYED</t>
+          <t>Content expanded in repo — NOT DEPLOYED</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
@@ -1151,7 +1166,7 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-07-26</t>
         </is>
       </c>
     </row>
@@ -1193,7 +1208,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>Updated in repo — NOT DEPLOYED</t>
+          <t>Content expanded in repo — NOT DEPLOYED</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -1213,7 +1228,7 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-07-26</t>
         </is>
       </c>
     </row>
@@ -1255,7 +1270,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>Updated in repo — NOT DEPLOYED</t>
+          <t>Content expanded in repo — NOT DEPLOYED</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1275,7 +1290,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-07-26</t>
         </is>
       </c>
     </row>
@@ -1317,7 +1332,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>Updated in repo — NOT DEPLOYED</t>
+          <t>Content expanded in repo — NOT DEPLOYED</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1337,7 +1352,7 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-07-26</t>
         </is>
       </c>
     </row>
@@ -1379,7 +1394,7 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>Updated in repo — NOT DEPLOYED</t>
+          <t>Content expanded in repo — NOT DEPLOYED</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -1399,7 +1414,7 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-07-26</t>
         </is>
       </c>
     </row>
@@ -1441,7 +1456,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>Updated in repo — NOT DEPLOYED</t>
+          <t>Content expanded in repo — NOT DEPLOYED</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1461,7 +1476,7 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-07-26</t>
         </is>
       </c>
     </row>
@@ -1503,7 +1518,7 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>Updated in repo — NOT DEPLOYED</t>
+          <t>Content expanded in repo — NOT DEPLOYED</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
@@ -1523,7 +1538,7 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-07-26</t>
         </is>
       </c>
     </row>
@@ -3808,7 +3823,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>City-templated title/description/OG using {cityLocative}; HreflangLinks; CleaningSeoSection (districts, FAQ, services, cross-links); CleaningSeoJsonLd (LocalBusiness/CleaningService + Service + BreadcrumbList + FAQPage) incl. rel=canonical.</t>
+          <t>City-templated title/description/OG using {cityLocative}; HreflangLinks; CleaningSeoSection (districts, FAQ, services, cross-links); CleaningSeoJsonLd (LocalBusiness/CleaningService + Service + BreadcrumbList + FAQPage) incl. rel=canonical. | 2026-07-26: 21-item city-adapted FAQ (payment options, key-handover act, upholstery/carpet/flowers, rental/one-off/neglected), Homies capitalised, per-city key streets, Book CTA to #order.</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -3870,7 +3885,7 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>Same as PL variant, EN copy and EN JSON-LD strings.</t>
+          <t>Same as PL variant, EN copy and EN JSON-LD strings. | 2026-07-26: 21-item city-adapted FAQ (payment options, key-handover act, upholstery/carpet/flowers, rental/one-off/neglected), Homies capitalised, per-city key streets, Book CTA to #order.</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -3932,7 +3947,7 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>City-templated title/description/OG using {cityLocative}; HreflangLinks; CleaningSeoSection (districts, FAQ, services, cross-links); CleaningSeoJsonLd (LocalBusiness/CleaningService + Service + BreadcrumbList + FAQPage) incl. rel=canonical.</t>
+          <t>City-templated title/description/OG using {cityLocative}; HreflangLinks; CleaningSeoSection (districts, FAQ, services, cross-links); CleaningSeoJsonLd (LocalBusiness/CleaningService + Service + BreadcrumbList + FAQPage) incl. rel=canonical. | 2026-07-26: 21-item city-adapted FAQ (payment options, key-handover act, upholstery/carpet/flowers, rental/one-off/neglected), Homies capitalised, per-city key streets, Book CTA to #order.</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -3994,7 +4009,7 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>Same as PL variant, EN copy and EN JSON-LD strings.</t>
+          <t>Same as PL variant, EN copy and EN JSON-LD strings. | 2026-07-26: 21-item city-adapted FAQ (payment options, key-handover act, upholstery/carpet/flowers, rental/one-off/neglected), Homies capitalised, per-city key streets, Book CTA to #order.</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -4056,7 +4071,7 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>City-templated title/description/OG using {cityLocative}; HreflangLinks; CleaningSeoSection (districts, FAQ, services, cross-links); CleaningSeoJsonLd (LocalBusiness/CleaningService + Service + BreadcrumbList + FAQPage) incl. rel=canonical.</t>
+          <t>City-templated title/description/OG using {cityLocative}; HreflangLinks; CleaningSeoSection (districts, FAQ, services, cross-links); CleaningSeoJsonLd (LocalBusiness/CleaningService + Service + BreadcrumbList + FAQPage) incl. rel=canonical. | 2026-07-26: 21-item city-adapted FAQ (payment options, key-handover act, upholstery/carpet/flowers, rental/one-off/neglected), Homies capitalised, per-city key streets, Book CTA to #order.</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -4118,7 +4133,7 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>Same as PL variant, EN copy and EN JSON-LD strings.</t>
+          <t>Same as PL variant, EN copy and EN JSON-LD strings. | 2026-07-26: 21-item city-adapted FAQ (payment options, key-handover act, upholstery/carpet/flowers, rental/one-off/neglected), Homies capitalised, per-city key streets, Book CTA to #order.</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -4180,7 +4195,7 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>City-templated title/description/OG using {cityLocative}; HreflangLinks; CleaningSeoSection (districts, FAQ, services, cross-links); CleaningSeoJsonLd (LocalBusiness/CleaningService + Service + BreadcrumbList + FAQPage) incl. rel=canonical.</t>
+          <t>City-templated title/description/OG using {cityLocative}; HreflangLinks; CleaningSeoSection (districts, FAQ, services, cross-links); CleaningSeoJsonLd (LocalBusiness/CleaningService + Service + BreadcrumbList + FAQPage) incl. rel=canonical. | 2026-07-26: 21-item city-adapted FAQ (payment options, key-handover act, upholstery/carpet/flowers, rental/one-off/neglected), Homies capitalised, per-city key streets, Book CTA to #order.</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -4242,7 +4257,7 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>Same as PL variant, EN copy and EN JSON-LD strings.</t>
+          <t>Same as PL variant, EN copy and EN JSON-LD strings. | 2026-07-26: 21-item city-adapted FAQ (payment options, key-handover act, upholstery/carpet/flowers, rental/one-off/neglected), Homies capitalised, per-city key streets, Book CTA to #order.</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -4304,7 +4319,7 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>City-templated title/description/OG using {cityLocative}; HreflangLinks; CleaningSeoSection (districts, FAQ, services, cross-links); CleaningSeoJsonLd (LocalBusiness/CleaningService + Service + BreadcrumbList + FAQPage) incl. rel=canonical.</t>
+          <t>City-templated title/description/OG using {cityLocative}; HreflangLinks; CleaningSeoSection (districts, FAQ, services, cross-links); CleaningSeoJsonLd (LocalBusiness/CleaningService + Service + BreadcrumbList + FAQPage) incl. rel=canonical. | 2026-07-26: 21-item city-adapted FAQ (payment options, key-handover act, upholstery/carpet/flowers, rental/one-off/neglected), Homies capitalised, per-city key streets, Book CTA to #order.</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -4366,7 +4381,7 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>Same as PL variant, EN copy and EN JSON-LD strings.</t>
+          <t>Same as PL variant, EN copy and EN JSON-LD strings. | 2026-07-26: 21-item city-adapted FAQ (payment options, key-handover act, upholstery/carpet/flowers, rental/one-off/neglected), Homies capitalised, per-city key streets, Book CTA to #order.</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -4428,7 +4443,7 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>City-templated title/description/OG using {cityLocative}; HreflangLinks; CleaningSeoSection (districts, FAQ, services, cross-links); CleaningSeoJsonLd (LocalBusiness/CleaningService + Service + BreadcrumbList + FAQPage) incl. rel=canonical.</t>
+          <t>City-templated title/description/OG using {cityLocative}; HreflangLinks; CleaningSeoSection (districts, FAQ, services, cross-links); CleaningSeoJsonLd (LocalBusiness/CleaningService + Service + BreadcrumbList + FAQPage) incl. rel=canonical. | 2026-07-26: 21-item city-adapted FAQ (payment options, key-handover act, upholstery/carpet/flowers, rental/one-off/neglected), Homies capitalised, per-city key streets, Book CTA to #order.</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
@@ -4490,7 +4505,7 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>Same as PL variant, EN copy and EN JSON-LD strings.</t>
+          <t>Same as PL variant, EN copy and EN JSON-LD strings. | 2026-07-26: 21-item city-adapted FAQ (payment options, key-handover act, upholstery/carpet/flowers, rental/one-off/neglected), Homies capitalised, per-city key streets, Book CTA to #order.</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
@@ -9450,7 +9465,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G27"/>
+  <dimension ref="A1:G35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -10458,6 +10473,302 @@
       <c r="G27" s="2" t="inlineStr">
         <is>
           <t>No test runner exists</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>ALL</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>Build</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>npm run lint (node:12)</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>Exit 0</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>28 prettier errors fixed + dead react/* disable removed; exit 0</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>ALL</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>Build</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>docker build (node:12, prod parity)</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>Exit 0, image builds</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>heyhomie-client:v2 built</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>CITY-*-PL/EN</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>Content</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>FAQ renders 21 items per city page</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>21 &lt;button&gt; FAQ items</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>container smoke /krakow, /en/krakow ... all 6 x2</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>CITY-*</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>Content</t>
+        </is>
+      </c>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>'Homies' capitalised, no lowercase 'homies'</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>0 lowercase occurrences</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="G31" s="2" t="inlineStr">
+        <is>
+          <t>grep of rendered HTML</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>CITY-*</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>SEO</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>Exactly one visible H1 per rendered city page</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>1 h1 (sr-only service+city)</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>PASS/REVIEW</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="G32" s="2" t="inlineStr">
+        <is>
+          <t>ServicesSlider sr-only H1; booking modals still emit h1 when opened — see R6</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>CITY-*</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>Content</t>
+        </is>
+      </c>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>Per-city key streets interpolated in 'how to enter details' answer</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>City-specific streets</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="G33" s="2" t="inlineStr">
+        <is>
+          <t>Krakow: Florianska... Warsaw: Marszalkowska...</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>CITY-*</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>SEO</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>JSON-LD FAQPage present with plain-text answers</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>ld+json, no markdown syntax</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="G34" s="2" t="inlineStr">
+        <is>
+          <t>stripMarkup feeds schema</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>CITY-*</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>Analytics/UX</t>
+        </is>
+      </c>
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>Book CTA + in-answer link target #order anchor</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
+        <is>
+          <t>#order scrolls to services</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F35" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="G35" s="2" t="inlineStr">
+        <is>
+          <t>span#order before ServicesContainer</t>
         </is>
       </c>
     </row>
@@ -10475,7 +10786,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G12"/>
+  <dimension ref="A1:G14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -10931,6 +11242,764 @@
         </is>
       </c>
     </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>CITY-*-PL, CITY-*-EN</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>CleaningSeoSection: FAQ 11-&gt;21 items, standard-vs-general fixed (windows = separate add-on), Homies capitalised, per-city key streets, payment 3 options, key-handover act, upholstery/carpet/flowers, how-to-order + how-to-enter-details, rental/one-off/neglected/after-death; primary Book CTA to #order; markdown-lite answer renderer; schema fed plain text.</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>Client content brief 2026-07-26 — richer, city-adapted, distinct from krakow.cleanwhale.pl and more complete.</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>In repo — NOT DEPLOYED</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>lint PASS, docker build PASS, smoke PASS (12 routes)</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>node:12 npm run lint exit 0; docker build exit 0; container smoke on all 6 cities x PL/EN</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>ALL (site-wide)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>Brand-canon design migration per heyhomie-shared/BRAND.md: fonts Quicksand/Lato -&gt; Manrope (+ Montserrat wordmark); palette mint #36F0C7-&gt;#77ECC8, pink #FF3C87-&gt;#EB4E87, ink #14133A-&gt;#141338, light #F4F7FF-&gt;#F6FBFF; tailwind theme tokens + _document font links updated; 82 component/page files + 42 SVG assets swept.</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>heyhomie-client was the only surface still on legacy tokens; mobile already migrated. Canon decided 2026-07 for all 4 surfaces.</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>In repo — NOT DEPLOYED</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>lint PASS (node:12), docker build PASS (v5)</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>node:12 npm run lint exit 0; docker build heyhomie-client:v5 exit 0; live tokens verified: Manrope+#77ECC8 present, Quicksand absent</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <tableParts count="1">
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E30"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="5" customWidth="1" min="1" max="1"/>
+    <col width="46" customWidth="1" min="2" max="2"/>
+    <col width="40" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="52" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Question (PL)</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Question (EN)</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>City-adaptive?</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>Czy obsługujecie wszystkie dzielnice {miasto}?</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>Do you cover all districts {city}?</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>locative</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>Homies capitalised</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>Czym rozni sie sprzatanie standardowe od generalnego?</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>Standard vs deep cleaning?</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>Windows = SEPARATE add-on; general adds oven/fridge/hood/inside cabinets</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>Jak zamowic usluge?</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>How do I place an order?</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>Book now -&gt; #order</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>Jak wskazac dane do zamowienia?</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>How do I provide the order details?</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>streets</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>Per-city streets; scope -&gt; Dalej/Continue -&gt; date/time -&gt; address -&gt; contact</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>Czy moge zmienic zakres uslugi po zlozeniu zamowienia?</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>Change scope after ordering?</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>Contact support before service</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>Czy musze byc w domu podczas sprzatania?</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>Do I have to be home?</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>Key-handover act w/ e-signature; inform support</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>Czy zapewniacie srodki czystosci?</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>Do you provide cleaning supplies?</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>No vacuum/bucket -&gt; support; permanent equip on recurring = Karcher only</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>Czy moge zamowic sprzatanie regularne?</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>Can I book recurring cleaning?</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>Weekly/biweekly/monthly; more frequent via support</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>Jak wyglada platnosc?</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>How does payment work?</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>3 options: subscription / bank transfer / Pay later (Apple Pay, Google Pay, BLIK)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>Czy akceptujecie zwierzeta?</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>Do you accept pets?</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>Inform support / mark on order</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>Co jesli nie bede zadowolony/a?</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>What if I am not happy?</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>Satisfaction guarantee; 'best home friend'</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>Czy wykonujecie jednorazowe sprzatanie mieszkan?</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>One-off apartment cleaning?</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>Yes; rates in price list at order</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>Czy moge zamowic sprzatanie pod wynajem?</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>Rental / end-of-tenancy cleaning?</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>Ready for next tenant</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>Sprzatanie mieszkan zaniedbanych i po najmie</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>Neglected apartments and after tenants</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>Tougher cases; de-duplicated from rental</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>Sprzatanie mieszkan po smierci i zlecenia specjalne</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>Cleaning after a death / special orders</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>NOT offered</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>Czyszczenie tapicerki i pranie mebli</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>Upholstery and furniture cleaning</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>Separate service; photo-&gt;support or in-app 'czyszczenie tapicerki'</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>Czy czyscicie dywany?</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>Do you clean carpets?</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>Pickup or on-site; B2B offices</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>Czym jest usluga dostawy kwiatow?</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>Flower delivery service?</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>Mixed bouquets delivery</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="n">
+        <v>19</v>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>Czy srodki czystosci sa bezpieczne dla dzieci i alergikow?</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>Products safe for children/allergies?</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>Eco, household-safe</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>Czy moge przelozyc lub odwolac wizyte?</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>Reschedule or cancel a visit?</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>Single visit via us; recurring from account</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="n">
+        <v>21</v>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>Jak policzyc liczbe okien do umycia?</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>How to count windows to clean?</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>Sashes / separate panes</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="n"/>
+      <c r="B23" s="2" t="n"/>
+      <c r="C23" s="2" t="n"/>
+      <c r="D23" s="2" t="n"/>
+      <c r="E23" s="2" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>KEY STREETS PER CITY (kept in original Polish in both locales)</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr"/>
+      <c r="C24" s="2" t="inlineStr"/>
+      <c r="D24" s="2" t="inlineStr"/>
+      <c r="E24" s="2" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>Krakow</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>Florianska, Karmelicka, Dluga, Aleja Pokoju</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr"/>
+      <c r="D25" s="2" t="inlineStr"/>
+      <c r="E25" s="2" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>Warszawa</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>Marszalkowska, Nowy Swiat, Pulawska, Aleje Jerozolimskie</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr"/>
+      <c r="D26" s="2" t="inlineStr"/>
+      <c r="E26" s="2" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>Poznan</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>Swiety Marcin, Glogowska, Polwiejska, Garbary</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr"/>
+      <c r="D27" s="2" t="inlineStr"/>
+      <c r="E27" s="2" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>Wroclaw</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>Swidnicka, Legnicka, Powstancow Slaskich, Grabiszynska</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr"/>
+      <c r="D28" s="2" t="inlineStr"/>
+      <c r="E28" s="2" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>Katowice</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>Mariacka, 3 Maja, Chorzowska, Warszawska</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr"/>
+      <c r="D29" s="2" t="inlineStr"/>
+      <c r="E29" s="2" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>Rzeszow</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>3 Maja, Grunwaldzka, Lubelska, Krakowska</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr"/>
+      <c r="D30" s="2" t="inlineStr"/>
+      <c r="E30" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <tableParts count="1">
